--- a/src/features/settlement/report/templates/신세계_거래명세표.xlsx
+++ b/src/features/settlement/report/templates/신세계_거래명세표.xlsx
@@ -624,94 +624,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
